--- a/sample_input.xlsx
+++ b/sample_input.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:D5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -429,27 +429,12 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>p_number_original</t>
+          <t>name</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>name</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>treatment</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>grupo</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>session</t>
+          <t>arm</t>
         </is>
       </c>
     </row>
@@ -466,27 +451,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>+15555550100</t>
+          <t>Priya</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Priya</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>3</t>
         </is>
       </c>
     </row>
@@ -503,27 +473,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>+15555550101</t>
+          <t>Arjun</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Arjun</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -540,27 +495,34 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>+15555550102</t>
+          <t>Meera</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Meera</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>1</t>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>whatsapp:+15555550103</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>RST2026-004</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Rahul</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>2</t>
         </is>
       </c>
     </row>
